--- a/Galar_Paths.xlsx
+++ b/Galar_Paths.xlsx
@@ -11511,7 +11511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11539,12 +11539,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Clear Route 4</t>
+          <t>Clear Route 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unlocks Route 5</t>
+          <t>Unlocks Route 2</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clear Route 5</t>
+          <t>Clear Route 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unlocks Galar Mine No. 2</t>
+          <t>Unlocks Rolling Fields</t>
         </is>
       </c>
     </row>
@@ -11573,12 +11573,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clear Galar Mine No. 2</t>
+          <t>Clear Rolling Fields</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unlocks Motostoke Outskirts</t>
+          <t>Unlocks Dappled Grove</t>
         </is>
       </c>
     </row>
@@ -11590,12 +11590,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clear Motostoke Outskirts</t>
+          <t>Clear Dappled Grove</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unlocks Watchtower Ruins</t>
+          <t>Unlocks West Lake Axewell</t>
         </is>
       </c>
     </row>
@@ -11607,12 +11607,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clear Route 6</t>
+          <t>Clear West Lake Axewell</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Unlocks Bridge Field</t>
+          <t>Unlocks East Lake Axewell</t>
         </is>
       </c>
     </row>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clear Bridge Field</t>
+          <t>Clear East Lake Axewell</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unlocks Stony Wilderness</t>
+          <t>Unlocks South Lake Miloch</t>
         </is>
       </c>
     </row>
@@ -11641,12 +11641,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clear Glimwood Tangle</t>
+          <t>Clear South Lake Miloch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unlocks Route 9</t>
+          <t>Unlocks North Lake Miloch</t>
         </is>
       </c>
     </row>
@@ -11658,12 +11658,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clear Route 9</t>
+          <t>Clear North Lake Miloch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unlocks Lake of Outrage</t>
+          <t>Unlocks Route 3</t>
         </is>
       </c>
     </row>
@@ -11675,12 +11675,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clear Lake of Outrage</t>
+          <t>Clear Route 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unlocks Route 10</t>
+          <t>Unlocks Galar Mine</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clear Route 10</t>
+          <t>Clear Galar Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unlocks Slumbering Weald 2</t>
+          <t>Unlocks Route 4</t>
         </is>
       </c>
     </row>
@@ -11709,333 +11709,877 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clear Slumbering Weald 2</t>
+          <t>Clear Route 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Unlocks Isle of Armor &amp; Crown Tundra</t>
+          <t>Unlocks Turffield Gym</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-1</t>
+          <t>Challenge 12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clear Fields of Honor</t>
+          <t>Clear Turffield Gym</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unlocks Soothing Wetlands</t>
+          <t>Unlocks Route 5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-2</t>
+          <t>Challenge 13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clear Soothing Wetlands</t>
+          <t>Clear Route 5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unlocks Forest of Focus</t>
+          <t>Unlocks Route 5 Daycare</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-3</t>
+          <t>Challenge 14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clear Forest of Focus</t>
+          <t>Clear Route 5 Daycare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unlocks Challenge Beach</t>
+          <t>Unlocks Galar Mine No. 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-4</t>
+          <t>Challenge 15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Clear Challenge Beach</t>
+          <t>Clear Galar Mine No. 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unlocks Brawlers' Cave</t>
+          <t>Unlocks Hulbury</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-5</t>
+          <t>Challenge 16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clear Brawlers' Cave</t>
+          <t>Clear Hulbury</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unlocks Challenge Road</t>
+          <t>Unlocks Hulbury Gym</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-6</t>
+          <t>Challenge 17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clear Challenge Road</t>
+          <t>Clear Hulbury Gym</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unlocks Training Lowlands</t>
+          <t>Unlocks Motostoke Outskirts</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-7</t>
+          <t>Challenge 18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Clear Training Lowlands</t>
+          <t>Clear Motostoke Outskirts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unlocks Warm-Up Tunnel</t>
+          <t>Unlocks Motostoke Gym</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-8</t>
+          <t>Challenge 19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clear Warm-Up Tunnel</t>
+          <t>Clear Motostoke Gym</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unlocks Workout Sea</t>
+          <t>Unlocks Watchtower Ruins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-9</t>
+          <t>Challenge 20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Clear Workout Sea</t>
+          <t>Clear Watchtower Ruins</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unlocks Stepping-Stone Sea</t>
+          <t>Unlocks Axew's Eye</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-10</t>
+          <t>Challenge 21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Clear Stepping-Stone Sea</t>
+          <t>Clear Axew's Eye</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unlocks Honeycalm Island</t>
+          <t>Unlocks Slumbering Weald</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-11</t>
+          <t>Challenge 22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clear Honeycalm Island</t>
+          <t>Clear Slumbering Weald</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Isle of Armor Completed</t>
+          <t>Unlocks Route 6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-1</t>
+          <t>Challenge 23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clear Slippery Slope</t>
+          <t>Clear Route 6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unlocks Frigid Sea</t>
+          <t>Unlocks Bridge Field Daycare</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-2</t>
+          <t>Challenge 24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clear Frigid Sea</t>
+          <t>Clear Bridge Field Daycare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unlocks Roaring-Sea Caves</t>
+          <t>Unlocks Bridge Field</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-3</t>
+          <t>Challenge 25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clear Roaring-Sea Caves</t>
+          <t>Clear Bridge Field</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Unlocks Lakeside Cave</t>
+          <t>Unlocks Stow-on-Side Gym</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-4</t>
+          <t>Challenge 26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clear Lakeside Cave</t>
+          <t>Clear Stow-on-Side Gym</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unlocks Old Cemetery</t>
+          <t>Unlocks Stony Wilderness</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-5</t>
+          <t>Challenge 27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clear Old Cemetery</t>
+          <t>Clear Stony Wilderness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unlocks Giant's Foot</t>
+          <t>Unlocks Dusty Bowl</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-6</t>
+          <t>Challenge 28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clear Giant's Foot</t>
+          <t>Clear Dusty Bowl</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unlocks Path to the Peak</t>
+          <t>Unlocks Giant's Cap</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-7</t>
+          <t>Challenge 29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Clear Path to the Peak</t>
+          <t>Clear Giant's Cap</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Unlocks Tunnel to the Top</t>
+          <t>Unlocks Hammerlocke Hills</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Challenge 30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Clear Hammerlocke Hills</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unlocks Motostoke Riverbank</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Challenge 31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Clear Motostoke Riverbank</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unlocks Route 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Challenge 32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Clear Route 7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Unlocks Route 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Challenge 33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Clear Route 8</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Unlocks Glimwood Tangle</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Challenge 34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Clear Glimwood Tangle</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Unlocks Ballonlea Gym</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Challenge 35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Clear Ballonlea Gym</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Unlocks Route 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Challenge 36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Clear Route 9</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Unlocks Circhester Gym</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Challenge 37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Clear Circhester Gym</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Unlocks Lake of Outrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Challenge 38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Clear Lake of Outrage</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Unlocks Spikemuth Gym</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Challenge 39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Clear Spikemuth Gym</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Unlocks Route 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Challenge 40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Clear Route 10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Unlocks Hammerlocke Gym</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Challenge 41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Clear Hammerlocke Gym</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Unlocks Slumbering Weald 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Challenge 42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Clear Slumbering Weald 2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Unlocks Pokemon League</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Challenge 43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Clear Pokemon League</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Unlocks Isle of Armor &amp; Crown Tundra</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Clear Fields of Honor</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Unlocks Soothing Wetlands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Clear Soothing Wetlands</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unlocks Forest of Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Clear Forest of Focus</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Unlocks Challenge Beach</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Clear Challenge Beach</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Unlocks Brawlers' Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Clear Brawlers' Cave</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Unlocks Challenge Road</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Clear Challenge Road</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Unlocks Training Lowlands</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Clear Training Lowlands</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Unlocks Warm-Up Tunnel</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Clear Warm-Up Tunnel</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Unlocks Workout Sea</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-9</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Clear Workout Sea</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Unlocks Stepping-Stone Sea</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Clear Stepping-Stone Sea</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Unlocks Honeycalm Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Extra Challenge $1-11</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Clear Honeycalm Island</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Isle of Armor Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Extra Challenge $2-1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Clear Slippery Slope</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Unlocks Frigid Sea</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Extra Challenge $2-2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Clear Frigid Sea</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Unlocks Roaring-Sea Caves</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Extra Challenge $2-3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Clear Roaring-Sea Caves</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Unlocks Lakeside Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Extra Challenge $2-4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Clear Lakeside Cave</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Unlocks Old Cemetery</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Extra Challenge $2-5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Clear Old Cemetery</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Unlocks Giant's Foot</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Extra Challenge $2-6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Clear Giant's Foot</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Unlocks Path to the Peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Extra Challenge $2-7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Clear Path to the Peak</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Unlocks Tunnel to the Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Extra Challenge $2-8</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Clear Tunnel to the Top</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Crown Tundra Completed</t>
         </is>

--- a/Galar_Paths.xlsx
+++ b/Galar_Paths.xlsx
@@ -1206,7 +1206,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tympole</t>
+          <t>Goldeen</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1230,7 +1230,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vanillite</t>
+          <t>Tympole</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Frillish</t>
+          <t>Wishiwashi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1278,7 +1278,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Krabby</t>
+          <t>Frillish</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wishiwashi</t>
+          <t>Remoraid</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1326,7 +1326,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Remoraid</t>
+          <t>Vanillite</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1350,7 +1350,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Goldeen</t>
+          <t>Klink</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1374,7 +1374,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Klink</t>
+          <t>Krabby</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2382,7 +2382,7 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Electrike</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2406,7 +2406,7 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ferroseed</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2430,7 +2430,7 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Joltik</t>
+          <t>Pumpkaboo</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2454,7 +2454,7 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Milcery</t>
+          <t>Meowth</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2478,7 +2478,7 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Pumpkaboo</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2502,7 +2502,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Meowth</t>
+          <t>Eevee</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2526,7 +2526,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Electrike</t>
+          <t>Cutiefly</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cutiefly</t>
+          <t>Ferroseed</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2574,7 +2574,7 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Eevee</t>
+          <t>Joltik</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Milcery</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3894,7 +3894,7 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Maractus</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -3918,7 +3918,7 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Helioptile</t>
+          <t>Heatmor</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -3942,7 +3942,7 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Axew</t>
+          <t>Torkoal</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -3966,7 +3966,7 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Drizzile</t>
+          <t>Silicobra</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -3990,7 +3990,7 @@
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Hawlucha</t>
+          <t>Thwackey</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4014,7 +4014,7 @@
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Heatmor</t>
+          <t>Hawlucha</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4038,7 +4038,7 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Thwackey</t>
+          <t>Drizzile</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4062,7 +4062,7 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Trapinch</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4086,7 +4086,7 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Dugtrio</t>
+          <t>Raboot</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4110,7 +4110,7 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Trapinch</t>
+          <t>Helioptile</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4134,7 +4134,7 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Silicobra</t>
+          <t>Dugtrio</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4158,7 +4158,7 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Raboot</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4182,7 +4182,7 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Yamask</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4206,7 +4206,7 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Yamask</t>
+          <t>Axew</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4230,7 +4230,7 @@
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Maractus</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4254,7 +4254,7 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Torkoal</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4278,7 +4278,7 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Mawile</t>
+          <t>Palpitoad</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4302,7 +4302,7 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Lanturn</t>
+          <t>Cufant</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4326,7 +4326,7 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Inkay</t>
+          <t>Cubchoo</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4350,7 +4350,7 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Qwilfish</t>
+          <t>Drednaw</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4374,7 +4374,7 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Poliwag</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4398,7 +4398,7 @@
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Drednaw</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4422,7 +4422,7 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Palpitoad</t>
+          <t>Qwilfish</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4446,7 +4446,7 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Cubchoo</t>
+          <t>Lanturn</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4470,7 +4470,7 @@
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Poliwag</t>
+          <t>Mawile</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4494,7 +4494,7 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cufant</t>
+          <t>Inkay</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5430,7 +5430,7 @@
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Seismitoad</t>
+          <t>Corviknight</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -5502,7 +5502,7 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Morpeko</t>
+          <t>Liepard</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -5526,7 +5526,7 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Meowstic</t>
+          <t>Karrablast</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -5550,7 +5550,7 @@
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Thievul</t>
+          <t>Morpeko</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -5574,7 +5574,7 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Liepard</t>
+          <t>Thievul</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -5598,7 +5598,7 @@
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Karrablast</t>
+          <t>Seismitoad</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -5646,7 +5646,7 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Corviknight</t>
+          <t>Toxel</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -5670,7 +5670,7 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Toxel</t>
+          <t>Meowstic</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -5694,7 +5694,7 @@
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Falinks</t>
+          <t>Togedemaru</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -5718,7 +5718,7 @@
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Boldore</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -5742,7 +5742,7 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Falinks</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -5766,7 +5766,7 @@
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Togedemaru</t>
+          <t>Rhyhorn</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -5790,7 +5790,7 @@
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Solrock</t>
+          <t>Boldore</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Lunatone</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -5838,7 +5838,7 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Sandaconda</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -5862,7 +5862,7 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Gurdurr</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -5886,7 +5886,7 @@
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Vullaby</t>
+          <t>Sandaconda</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -5934,7 +5934,7 @@
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Lunatone</t>
+          <t>Vullaby</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -5958,7 +5958,7 @@
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Rhyhorn</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -5982,7 +5982,7 @@
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Solrock</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6006,7 +6006,7 @@
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Gurdurr</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6030,7 +6030,7 @@
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Morgrem</t>
+          <t>Hattrem</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6054,7 +6054,7 @@
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Oranguru</t>
+          <t>Indeedee</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6078,7 +6078,7 @@
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Sinistea</t>
+          <t>Phantump</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6102,7 +6102,7 @@
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Phantump</t>
+          <t>Ponyta</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6150,7 +6150,7 @@
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Ponyta</t>
+          <t>Morgrem</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6174,7 +6174,7 @@
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Passimian</t>
+          <t>Oranguru</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6198,7 +6198,7 @@
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Indeedee</t>
+          <t>Sinistea</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6222,7 +6222,7 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Hattrem</t>
+          <t>Passimian</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -6462,7 +6462,7 @@
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Copperajah</t>
+          <t>Eiscue</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -6486,7 +6486,7 @@
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Vanilluxe</t>
+          <t>Ditto</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -6510,7 +6510,7 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Bisharp</t>
+          <t>Duraludon</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -6534,7 +6534,7 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Klinklang</t>
+          <t>Doublade</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -6558,7 +6558,7 @@
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Eiscue</t>
+          <t>Golurk</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -6582,7 +6582,7 @@
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Duraludon</t>
+          <t>Vanilluxe</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Golurk</t>
+          <t>Copperajah</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -6630,7 +6630,7 @@
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Doublade</t>
+          <t>Klinklang</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -6654,7 +6654,7 @@
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Ditto</t>
+          <t>Bisharp</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -6678,7 +6678,7 @@
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Abomasnow</t>
+          <t>Snom</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -6702,7 +6702,7 @@
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Snover</t>
+          <t>Darumaka</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -6726,7 +6726,7 @@
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Darumaka</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -6750,7 +6750,7 @@
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Snom</t>
+          <t>Beartic</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -6774,7 +6774,7 @@
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Cubchoo</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -6798,7 +6798,7 @@
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Cubchoo</t>
+          <t>Abomasnow</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -6822,7 +6822,7 @@
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Beartic</t>
+          <t>Mr. Mime</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -6870,7 +6870,7 @@
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Mr. Mime</t>
+          <t>Snover</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>70-100</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>70-100</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>70-100</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>70-100</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>70-100</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>70-100</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>70-100</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7072,26 +7072,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Energy Plant</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Fields of Honor</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Zacian</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="278">
@@ -7102,212 +7098,200 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Energy Plant</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Fields of Honor</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Zamazenta</t>
+          <t>Jigglypuff</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>E2-1</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Rock Peak Ruins</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Centiskorch</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Iceberg Ruins</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Hatterene</t>
+          <t>Abra</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>E2-3</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Iron Ruins</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Toxtricity</t>
+          <t>Klefki</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>E2-4</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Split-Decision Ruins</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Fields of Honor</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Regieleki</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>E2-4</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Split-Decision Ruins</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Fields of Honor</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Regidrago</t>
+          <t>Kubfu</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Smoochum</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>77-87</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Amaura</t>
+          <t>Oranguru</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -7317,23 +7301,23 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Cryogonal</t>
+          <t>Foongus</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -7343,23 +7327,23 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -7369,49 +7353,49 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Snom</t>
+          <t>Karrablast</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F288" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Greedent</t>
+          <t>Emolga</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -7421,23 +7405,23 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Mime Jr.</t>
+          <t>Venipede</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -7447,49 +7431,49 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F291" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Jynx</t>
+          <t>Beldum</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F292" t="n">
@@ -7499,49 +7483,49 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Nidoran♂</t>
+          <t>Passimian</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>85-94</t>
         </is>
       </c>
       <c r="F293" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Heracross</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -7551,23 +7535,23 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Vanillite</t>
+          <t>Lillipup</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7577,23 +7561,23 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Sinistea</t>
+          <t>Pinsir</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -7603,49 +7587,49 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Scyther</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F297" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Drakloak</t>
+          <t>Sharpedo</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -7655,23 +7639,23 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Mime Jr.</t>
+          <t>Miltank</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -7681,49 +7665,49 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Karrablast</t>
+          <t>Tauros</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F300" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Nidoran♀</t>
+          <t>Carvanha</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -7733,101 +7717,109 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E1-4</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
+          <t>Training Lowlands</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Frosmoth</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>92-100</t>
         </is>
       </c>
       <c r="F302" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E1-5</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr"/>
+          <t>Energy Plant</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Snom</t>
+          <t>Zacian</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F303" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E1-5</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
+          <t>Energy Plant</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Zamazenta</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F304" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Lickitung</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -7837,83 +7829,75 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>E3-4</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Crown Shrine</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Brawlers' Cave</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Glastrier</t>
+          <t>Whismur</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F306" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>E3-4</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Crown Shrine</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Brawlers' Cave</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Spectrier</t>
+          <t>Psyduck</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F307" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Spheal</t>
+          <t>Azurill</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -7923,23 +7907,23 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Feebas</t>
+          <t>Woobat</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -7949,49 +7933,49 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Carbink</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Mienfoo</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8001,603 +7985,603 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Larvitar</t>
+          <t>Skarmory</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Omanyte</t>
+          <t>Rockruff</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Deino</t>
+          <t>Dwebble</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Roggenrola</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Kabuto</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Gyarados</t>
+          <t>Salandit</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Dhelmise</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Avalugg</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F319" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Tirtouga</t>
+          <t>Sandshrew</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F320" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Lapras</t>
+          <t>Cubone</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F321" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Kangaskhan</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F322" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Cryogonal</t>
+          <t>Torkoal</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F323" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Eiscue</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F324" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E2-4</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Potbottom Desert</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Bagon</t>
+          <t>Sirfetch'd</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>82-89</t>
         </is>
       </c>
       <c r="F325" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E2-5</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Rock Peak Ruins</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Gible</t>
+          <t>Coalossal</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E2-6</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Iceberg Ruins</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Clefairy</t>
+          <t>Dubwool</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E2-7</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Iron Ruins</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Snorunt</t>
+          <t>Dracovish</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E2-8</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
+          <t>Split-Decision Ruins</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Regieleki</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E2-8</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
+          <t>Split-Decision Ruins</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Regidrago</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Carbink</t>
+          <t>Smoochum</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>E4-4</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Tower Summit</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Slippery Slope</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Calyrex</t>
+          <t>Snom</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>E4-4</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Tower Summit</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Slippery Slope</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Eternatus</t>
+          <t>Mime Jr.</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Claydol</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8607,205 +8591,205 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Archen</t>
+          <t>Greedent</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Copperajah</t>
+          <t>Jynx</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Stonjourner</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F337" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Cryogonal</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F338" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Cryogonal</t>
+          <t>Amaura</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F339" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Mime Jr.</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Giant's Foot</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Aron</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8815,23 +8799,23 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Carkol</t>
+          <t>Nidoran♂</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -8841,75 +8825,75 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Sableye</t>
+          <t>Drakloak</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Noivern</t>
+          <t>Nidoran♀</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Karrablast</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F346" t="n">
@@ -8919,176 +8903,168 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Carbink</t>
+          <t>Vanillite</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F347" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Mawile</t>
+          <t>Sinistea</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F348" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Path to the Peak</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Ferroseed</t>
+          <t>Frosmoth</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F349" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Lakeside Cave</t>
+          <t>Path to the Peak</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Snom</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F350" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Dyna Tree Hill</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Path to the Peak</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Articuno</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F351" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Dyna Tree Hill</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Path to the Peak</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Zapdos</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F352" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E3-4</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Dyna Tree Hill</t>
+          <t>Crown Shrine</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9098,7 +9074,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Moltres</t>
+          <t>Glastrier</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9107,55 +9083,59 @@
         </is>
       </c>
       <c r="F353" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E3-4</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr"/>
+          <t>Crown Shrine</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Spectrier</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Jigglypuff</t>
+          <t>Carbink</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -9165,23 +9145,23 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -9191,23 +9171,23 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Abra</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F357" t="n">
@@ -9217,49 +9197,49 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Klefki</t>
+          <t>Omanyte</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F358" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Deino</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F359" t="n">
@@ -9269,23 +9249,23 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Kubfu</t>
+          <t>Spheal</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F360" t="n">
@@ -9295,23 +9275,23 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>E6-1</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Larvitar</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F361" t="n">
@@ -9321,75 +9301,75 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Bouffalant</t>
+          <t>Feebas</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Skwovet</t>
+          <t>Kabuto</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>70-82</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Applin</t>
+          <t>Gyarados</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F364" t="n">
@@ -9399,23 +9379,23 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Shelmet</t>
+          <t>Dhelmise</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F365" t="n">
@@ -9425,75 +9405,75 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Lickitung</t>
+          <t>Avalugg</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Tirtouga</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F367" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Lapras</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F368" t="n">
@@ -9503,127 +9483,127 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Wooper</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>E6-2</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Dunsparce</t>
+          <t>Cryogonal</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F370" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Eiscue</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>80-92</t>
         </is>
       </c>
       <c r="F371" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Foongus</t>
+          <t>Bagon</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F372" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Oranguru</t>
+          <t>Gible</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9633,23 +9613,23 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Emolga</t>
+          <t>Clefairy</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F374" t="n">
@@ -9659,75 +9639,75 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Karrablast</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F375" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Passimian</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Venipede</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9737,231 +9717,239 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Beldum</t>
+          <t>Carbink</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>E6-3</t>
+          <t>E4-4</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr"/>
+          <t>Tower Summit</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Calyrex</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E4-4</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr"/>
+          <t>Tower Summit</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Pinsir</t>
+          <t>Eternatus</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Carvanha</t>
+          <t>Magnemite</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Lillipup</t>
+          <t>Dedenne</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F382" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Heracross</t>
+          <t>Psyduck</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Tauros</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Sharpedo</t>
+          <t>Morpeko</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>70-76</t>
         </is>
       </c>
       <c r="F386" t="n">
@@ -9971,309 +9959,309 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Scyther</t>
+          <t>Clauncher</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F387" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>E6-4</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Miltank</t>
+          <t>Octillery</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>E6-5</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Whismur</t>
+          <t>Tentacool</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>E6-5</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Psyduck</t>
+          <t>Skrelp</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>E6-5</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Azurill</t>
+          <t>Remoraid</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>E6-5</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Woobat</t>
+          <t>Clawitzer</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>E6-5</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Lickitung</t>
+          <t>Magikarp</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>E6-5</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Mantyke</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>E7-1</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Magnemite</t>
+          <t>Dragalge</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>74-80</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>E7-1</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Dedenne</t>
+          <t>Exeggcute</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>E7-1</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Psyduck</t>
+          <t>Flapple</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>E7-1</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Appletun</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -10283,23 +10271,23 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>E7-1</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Morpeko</t>
+          <t>Wingull</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F399" t="n">
@@ -10309,23 +10297,23 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>E7-1</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Skwovet</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F400" t="n">
@@ -10335,257 +10323,257 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Clawitzer</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Mantyke</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Remoraid</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>78-84</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-4</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Magikarp</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>82-89</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-4</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Octillery</t>
+          <t>Petilil</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>82-89</t>
         </is>
       </c>
       <c r="F405" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-4</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Tentacool</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>82-89</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-4</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Clauncher</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>82-89</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-4</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Dragalge</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>82-89</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>E7-2</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Skrelp</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Exeggcute</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10595,23 +10583,23 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Flapple</t>
+          <t>Skwovet</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10621,23 +10609,23 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Appletun</t>
+          <t>Bouffalant</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10647,49 +10635,49 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Wingull</t>
+          <t>Applin</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Skwovet</t>
+          <t>Wooper</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10699,23 +10687,23 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -10725,153 +10713,153 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Shelmet</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>E7-3</t>
+          <t>E5-5</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Dunsparce</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>E7-4</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Claydol</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>E7-4</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Petilil</t>
+          <t>Archen</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F419" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>E7-4</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Copperajah</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F420" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>E7-4</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Stonjourner</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F421" t="n">
@@ -10881,127 +10869,127 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>E7-4</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>100-100</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Mienfoo</t>
+          <t>Cryogonal</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Skarmory</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-6</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Giant's Foot</t>
         </is>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Rockruff</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>91-97</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Dwebble</t>
+          <t>Aron</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11011,272 +10999,280 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Roggenrola</t>
+          <t>Carkol</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Sableye</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Salandit</t>
+          <t>Noivern</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>E8-1</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Carbink</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>70-87</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>E8-2</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Sandshrew</t>
+          <t>Mawile</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>E8-2</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Cubone</t>
+          <t>Ferroseed</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>E8-2</t>
+          <t>E5-7</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Lakeside Cave</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Kangaskhan</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>95-100</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>E8-2</t>
+          <t>E5-8</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr"/>
+          <t>Dyna Tree Hill</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Torkoal</t>
+          <t>Articuno</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>E8-2</t>
+          <t>E5-8</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr"/>
+          <t>Dyna Tree Hill</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Zapdos</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>85-100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>E8-3</t>
+          <t>E5-8</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Potbottom Desert</t>
+          <t>Dyna Tree Hill</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -11286,7 +11282,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Urshifu</t>
+          <t>Moltres</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -11295,7 +11291,7 @@
         </is>
       </c>
       <c r="F437" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -12039,7 +12035,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Unlocks all DLC Chains (Slumbering Weald 2, Rock Peak Ruins, Slippery Slope, etc.)</t>
+          <t>Unlocks all 5 DLC Chains (Heroes, Regis, Steeds, Kings, Birds)</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12052,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Unlocks Energy Plant</t>
+          <t>Unlocks Fields of Honor</t>
         </is>
       </c>
     </row>
@@ -12068,471 +12064,471 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clear Energy Plant</t>
+          <t>Clear Fields of Honor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Completed Zacian &amp; Zamazenta (Defeated Zacian &amp; Zamazenta)</t>
+          <t>Unlocks Forest of Focus</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-1</t>
+          <t>Extra Challenge $1-3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Clear Rock Peak Ruins</t>
+          <t>Clear Forest of Focus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unlocks Iceberg Ruins</t>
+          <t>Unlocks Training Lowlands</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-2</t>
+          <t>Extra Challenge $1-4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Clear Iceberg Ruins</t>
+          <t>Clear Training Lowlands</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unlocks Iron Ruins</t>
+          <t>Unlocks Energy Plant</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-3</t>
+          <t>Extra Challenge $1-5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clear Iron Ruins</t>
+          <t>Clear Energy Plant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Unlocks Split-Decision Ruins</t>
+          <t>Completed Heroes of Galar (Defeated Zacian &amp; Zamazenta)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-4</t>
+          <t>Extra Challenge $2-1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clear Split-Decision Ruins</t>
+          <t>Clear Brawlers' Cave</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Completed Regis (Defeated Regieleki &amp; Regidrago)</t>
+          <t>Unlocks Challenge Road</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-1</t>
+          <t>Extra Challenge $2-2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clear Slippery Slope</t>
+          <t>Clear Challenge Road</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unlocks Old Cemetery</t>
+          <t>Unlocks Warm-Up Tunnel</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-2</t>
+          <t>Extra Challenge $2-3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clear Old Cemetery</t>
+          <t>Clear Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unlocks Path to the Peak</t>
+          <t>Unlocks Potbottom Desert</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-3</t>
+          <t>Extra Challenge $2-4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Clear Path to the Peak</t>
+          <t>Clear Potbottom Desert</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unlocks Crown Shrine</t>
+          <t>Unlocks Rock Peak Ruins</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-4</t>
+          <t>Extra Challenge $2-5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clear Crown Shrine</t>
+          <t>Clear Rock Peak Ruins</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Completed Horses (Defeated Glastrier &amp; Spectrier)</t>
+          <t>Unlocks Iceberg Ruins</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-1</t>
+          <t>Extra Challenge $2-6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clear Roaring-Sea Caves</t>
+          <t>Clear Iceberg Ruins</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Unlocks Frigid Sea</t>
+          <t>Unlocks Iron Ruins</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-2</t>
+          <t>Extra Challenge $2-7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clear Frigid Sea</t>
+          <t>Clear Iron Ruins</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unlocks Tunnel to the Top</t>
+          <t>Unlocks Split-Decision Ruins</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-3</t>
+          <t>Extra Challenge $2-8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Clear Tunnel to the Top</t>
+          <t>Clear Split-Decision Ruins</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unlocks Tower Summit</t>
+          <t>Completed The Regis (Defeated Regieleki &amp; Regidrago)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-4</t>
+          <t>Extra Challenge $3-1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clear Tower Summit</t>
+          <t>Clear Slippery Slope</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Completed Kings (Defeated Calyrex &amp; Eternatus)</t>
+          <t>Unlocks Old Cemetery</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-1</t>
+          <t>Extra Challenge $3-2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Clear Giant's Foot</t>
+          <t>Clear Old Cemetery</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Unlocks Lakeside Cave</t>
+          <t>Unlocks Path to the Peak</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-2</t>
+          <t>Extra Challenge $3-3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Clear Lakeside Cave</t>
+          <t>Clear Path to the Peak</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unlocks Dyna Tree Hill</t>
+          <t>Unlocks Crown Shrine</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-3</t>
+          <t>Extra Challenge $3-4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clear Dyna Tree Hill</t>
+          <t>Clear Crown Shrine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Completed Birds (Defeated Articuno &amp; Zapdos &amp; Moltres)</t>
+          <t>Completed The Steeds (Defeated Glastrier &amp; Spectrier)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Extra Challenge $6-1</t>
+          <t>Extra Challenge $4-1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Clear Fields of Honor</t>
+          <t>Clear Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unlocks Soothing Wetlands</t>
+          <t>Unlocks Frigid Sea</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Extra Challenge $6-2</t>
+          <t>Extra Challenge $4-2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Clear Soothing Wetlands</t>
+          <t>Clear Frigid Sea</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Unlocks Forest of Focus</t>
+          <t>Unlocks Tunnel to the Top</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Extra Challenge $6-3</t>
+          <t>Extra Challenge $4-3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Clear Forest of Focus</t>
+          <t>Clear Tunnel to the Top</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unlocks Training Lowlands</t>
+          <t>Unlocks Tower Summit</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Extra Challenge $6-4</t>
+          <t>Extra Challenge $4-4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Clear Training Lowlands</t>
+          <t>Clear Tower Summit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Unlocks Brawlers' Cave</t>
+          <t>Completed The Kings (Defeated Calyrex &amp; Eternatus)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Extra Challenge $6-5</t>
+          <t>Extra Challenge $5-1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Clear Brawlers' Cave</t>
+          <t>Clear Challenge Beach</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Completed Isle of Armor Plains</t>
+          <t>Unlocks Workout Sea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Extra Challenge $7-1</t>
+          <t>Extra Challenge $5-2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clear Challenge Beach</t>
+          <t>Clear Workout Sea</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unlocks Workout Sea</t>
+          <t>Unlocks Stepping-Stone Sea</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Extra Challenge $7-2</t>
+          <t>Extra Challenge $5-3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Clear Workout Sea</t>
+          <t>Clear Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unlocks Stepping-Stone Sea</t>
+          <t>Unlocks Honeycalm Island</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Extra Challenge $7-3</t>
+          <t>Extra Challenge $5-4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Clear Stepping-Stone Sea</t>
+          <t>Clear Honeycalm Island</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unlocks Honeycalm Island</t>
+          <t>Unlocks Soothing Wetlands</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Extra Challenge $7-4</t>
+          <t>Extra Challenge $5-5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Clear Honeycalm Island</t>
+          <t>Clear Soothing Wetlands</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Completed Isle of Armor Sea</t>
+          <t>Unlocks Giant's Foot</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Extra Challenge $8-1</t>
+          <t>Extra Challenge $5-6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Clear Challenge Road</t>
+          <t>Clear Giant's Foot</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unlocks Warm-Up Tunnel</t>
+          <t>Unlocks Lakeside Cave</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Extra Challenge $8-2</t>
+          <t>Extra Challenge $5-7</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Clear Warm-Up Tunnel</t>
+          <t>Clear Lakeside Cave</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unlocks Potbottom Desert</t>
+          <t>Unlocks Dyna Tree Hill</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Extra Challenge $8-3</t>
+          <t>Extra Challenge $5-8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Clear Potbottom Desert</t>
+          <t>Clear Dyna Tree Hill</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Completed Isle of Armor Mountains (Defeated Urshifu)</t>
+          <t>Completed The Legendary Birds (Defeated Articuno &amp; Zapdos &amp; Moltres)</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12638,6 +12634,28 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Urshifu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fighting/Dark</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No (Excluded per instructions)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Galar_Paths.xlsx
+++ b/Galar_Paths.xlsx
@@ -1182,7 +1182,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Delibird</t>
+          <t>Remoraid</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1206,7 +1206,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Goldeen</t>
+          <t>Vanillite</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1230,7 +1230,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tympole</t>
+          <t>Klink</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wishiwashi</t>
+          <t>Tympole</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Remoraid</t>
+          <t>Delibird</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1326,7 +1326,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vanillite</t>
+          <t>Krabby</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1350,7 +1350,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Klink</t>
+          <t>Wishiwashi</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1374,7 +1374,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Krabby</t>
+          <t>Goldeen</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2382,7 +2382,7 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Electrike</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2406,7 +2406,7 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Pumpkaboo</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2430,7 +2430,7 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Pumpkaboo</t>
+          <t>Milcery</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2454,7 +2454,7 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Meowth</t>
+          <t>Electrike</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2478,7 +2478,7 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Ferroseed</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2502,7 +2502,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Eevee</t>
+          <t>Joltik</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2526,7 +2526,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cutiefly</t>
+          <t>Eevee</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ferroseed</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2574,7 +2574,7 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Joltik</t>
+          <t>Meowth</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Milcery</t>
+          <t>Cutiefly</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3894,7 +3894,7 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Raboot</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -3918,7 +3918,7 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Heatmor</t>
+          <t>Maractus</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -3942,7 +3942,7 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Torkoal</t>
+          <t>Thwackey</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -3966,7 +3966,7 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Silicobra</t>
+          <t>Heatmor</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -3990,7 +3990,7 @@
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Thwackey</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4014,7 +4014,7 @@
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Hawlucha</t>
+          <t>Dugtrio</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4038,7 +4038,7 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Drizzile</t>
+          <t>Torkoal</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4062,7 +4062,7 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Trapinch</t>
+          <t>Drizzile</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4086,7 +4086,7 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Raboot</t>
+          <t>Yamask</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4110,7 +4110,7 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Helioptile</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4134,7 +4134,7 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Dugtrio</t>
+          <t>Trapinch</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4158,7 +4158,7 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Hawlucha</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4182,7 +4182,7 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Yamask</t>
+          <t>Silicobra</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4230,7 +4230,7 @@
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Maractus</t>
+          <t>Helioptile</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4278,7 +4278,7 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Palpitoad</t>
+          <t>Inkay</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4302,7 +4302,7 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cufant</t>
+          <t>Drednaw</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4326,7 +4326,7 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Cubchoo</t>
+          <t>Cufant</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4350,7 +4350,7 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Drednaw</t>
+          <t>Palpitoad</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4374,7 +4374,7 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Poliwag</t>
+          <t>Cubchoo</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4398,7 +4398,7 @@
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Poliwag</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4422,7 +4422,7 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Qwilfish</t>
+          <t>Lanturn</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4446,7 +4446,7 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Lanturn</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4470,7 +4470,7 @@
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mawile</t>
+          <t>Qwilfish</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4494,7 +4494,7 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Inkay</t>
+          <t>Mawile</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5430,7 +5430,7 @@
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Corviknight</t>
+          <t>Thievul</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -5454,7 +5454,7 @@
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Shelmet</t>
+          <t>Meowstic</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -5478,7 +5478,7 @@
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Galvantula</t>
+          <t>Perrserker</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -5502,7 +5502,7 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Liepard</t>
+          <t>Corviknight</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -5526,7 +5526,7 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Karrablast</t>
+          <t>Galvantula</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -5550,7 +5550,7 @@
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Morpeko</t>
+          <t>Shelmet</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -5574,7 +5574,7 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Thievul</t>
+          <t>Morpeko</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -5622,7 +5622,7 @@
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Perrserker</t>
+          <t>Liepard</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -5670,7 +5670,7 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Meowstic</t>
+          <t>Karrablast</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -5694,7 +5694,7 @@
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Togedemaru</t>
+          <t>Drapion</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -5718,7 +5718,7 @@
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Falinks</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -5742,7 +5742,7 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Falinks</t>
+          <t>Togedemaru</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -5790,7 +5790,7 @@
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Boldore</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Lunatone</t>
+          <t>Sandaconda</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -5838,7 +5838,7 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Vullaby</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -5862,7 +5862,7 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Gurdurr</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -5886,7 +5886,7 @@
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Sandaconda</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Drapion</t>
+          <t>Boldore</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -5934,7 +5934,7 @@
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Vullaby</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -5958,7 +5958,7 @@
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Solrock</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -5982,7 +5982,7 @@
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Solrock</t>
+          <t>Lunatone</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6006,7 +6006,7 @@
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Gurdurr</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6054,7 +6054,7 @@
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Indeedee</t>
+          <t>Oranguru</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6078,7 +6078,7 @@
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Phantump</t>
+          <t>Sinistea</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6102,7 +6102,7 @@
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Ponyta</t>
+          <t>Phantump</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6150,7 +6150,7 @@
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Morgrem</t>
+          <t>Indeedee</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6174,7 +6174,7 @@
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Oranguru</t>
+          <t>Passimian</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6198,7 +6198,7 @@
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Sinistea</t>
+          <t>Morgrem</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6222,7 +6222,7 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Passimian</t>
+          <t>Ponyta</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -6486,7 +6486,7 @@
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Ditto</t>
+          <t>Bisharp</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -6510,7 +6510,7 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Duraludon</t>
+          <t>Ditto</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -6534,7 +6534,7 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Doublade</t>
+          <t>Vanilluxe</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -6558,7 +6558,7 @@
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Golurk</t>
+          <t>Duraludon</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -6582,7 +6582,7 @@
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Vanilluxe</t>
+          <t>Doublade</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -6654,7 +6654,7 @@
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Bisharp</t>
+          <t>Golurk</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -6678,7 +6678,7 @@
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Snom</t>
+          <t>Darumaka</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -6702,7 +6702,7 @@
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Darumaka</t>
+          <t>Snover</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -6726,7 +6726,7 @@
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Beartic</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -6750,7 +6750,7 @@
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Beartic</t>
+          <t>Cubchoo</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -6774,7 +6774,7 @@
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Cubchoo</t>
+          <t>Stonjourner</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -6798,7 +6798,7 @@
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Abomasnow</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -6822,7 +6822,7 @@
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Mr. Mime</t>
+          <t>Snom</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -6846,7 +6846,7 @@
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Stonjourner</t>
+          <t>Abomasnow</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -6870,7 +6870,7 @@
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Snover</t>
+          <t>Mr. Mime</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -6885,23 +6885,23 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>E1-1</t>
+          <t>EP1-1</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Slumbering Weald 2</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Orbeetle</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>15-20</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -6911,23 +6911,23 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>E1-1</t>
+          <t>EP1-1</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Slumbering Weald 2</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Butterfree</t>
+          <t>Jigglypuff</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>15-20</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -6937,23 +6937,23 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>E1-1</t>
+          <t>EP1-1</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Slumbering Weald 2</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Whiscash</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>15-20</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -6963,23 +6963,23 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>E1-1</t>
+          <t>EP1-1</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Slumbering Weald 2</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Barboach</t>
+          <t>Abra</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>15-20</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -6989,23 +6989,23 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>E1-1</t>
+          <t>EP1-1</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Slumbering Weald 2</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Corviknight</t>
+          <t>Klefki</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>15-20</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7015,23 +7015,23 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>E1-1</t>
+          <t>EP1-1</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Slumbering Weald 2</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Stunfisk</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>15-20</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7041,23 +7041,23 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>E1-1</t>
+          <t>EP1-1</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Slumbering Weald 2</t>
+          <t>Fields of Honor</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Magikarp</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>15-20</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7067,23 +7067,23 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Skwovet</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7093,23 +7093,23 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Jigglypuff</t>
+          <t>Shelmet</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7119,23 +7119,23 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Lickitung</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7145,23 +7145,23 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Abra</t>
+          <t>Bouffalant</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7171,23 +7171,23 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Klefki</t>
+          <t>Wooper</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7197,23 +7197,23 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Dunsparce</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7223,23 +7223,23 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Kubfu</t>
+          <t>Applin</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7249,59 +7249,59 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>E1-2</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Fields of Honor</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>77-87</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-2</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Forest of Focus</t>
+          <t>Soothing Wetlands</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Oranguru</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7312,12 +7312,12 @@
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Foongus</t>
+          <t>Beldum</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -7327,7 +7327,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -7353,7 +7353,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7364,12 +7364,12 @@
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Karrablast</t>
+          <t>Oranguru</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -7379,7 +7379,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7390,22 +7390,22 @@
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Emolga</t>
+          <t>Foongus</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -7431,7 +7431,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7442,12 +7442,12 @@
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Emolga</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -7457,7 +7457,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7468,22 +7468,22 @@
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Beldum</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>E1-3</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>85-94</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -7509,33 +7509,33 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-3</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Training Lowlands</t>
+          <t>Forest of Focus</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Heracross</t>
+          <t>Karrablast</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="F294" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7546,12 +7546,12 @@
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Lillipup</t>
+          <t>Scyther</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7561,7 +7561,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7572,12 +7572,12 @@
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Pinsir</t>
+          <t>Carvanha</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -7587,7 +7587,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7598,12 +7598,12 @@
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Scyther</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -7613,7 +7613,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7624,22 +7624,22 @@
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Sharpedo</t>
+          <t>Lillipup</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F298" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7650,12 +7650,12 @@
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Miltank</t>
+          <t>Pinsir</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -7665,7 +7665,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7676,12 +7676,12 @@
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Tauros</t>
+          <t>Miltank</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -7691,7 +7691,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7702,22 +7702,22 @@
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Carvanha</t>
+          <t>Tauros</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F301" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>E1-4</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7728,12 +7728,12 @@
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Heracross</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>92-100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -7743,42 +7743,38 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>E1-5</t>
+          <t>EP1-4</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Energy Plant</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Training Lowlands</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Zacian</t>
+          <t>Sharpedo</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="F303" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>E1-5</t>
+          <t>EP1-5</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Energy Plant</t>
+          <t>Master Dojo</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7788,38 +7784,38 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Zamazenta</t>
+          <t>Kubfu</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30-30</t>
         </is>
       </c>
       <c r="F304" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>E2-1</t>
+          <t>EP2-1</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Lickitung</t>
+          <t>Psyduck</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>40-47</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -7829,23 +7825,23 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>E2-1</t>
+          <t>EP2-1</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Whismur</t>
+          <t>Magnemite</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>40-47</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -7855,23 +7851,23 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>E2-1</t>
+          <t>EP2-1</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Psyduck</t>
+          <t>Dedenne</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>40-47</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -7881,23 +7877,23 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>E2-1</t>
+          <t>EP2-1</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Azurill</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>40-47</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -7907,23 +7903,23 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>E2-1</t>
+          <t>EP2-1</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Woobat</t>
+          <t>Morpeko</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>40-47</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -7933,12 +7929,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>E2-1</t>
+          <t>EP2-1</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Brawlers' Cave</t>
+          <t>Challenge Beach</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -7949,7 +7945,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>40-47</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -7959,23 +7955,23 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Mienfoo</t>
+          <t>Clawitzer</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -7985,23 +7981,23 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Skarmory</t>
+          <t>Dragalge</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8011,23 +8007,23 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Rockruff</t>
+          <t>Magikarp</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8037,23 +8033,23 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Dwebble</t>
+          <t>Clauncher</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8063,23 +8059,23 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Roggenrola</t>
+          <t>Remoraid</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8089,23 +8085,23 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Gyarados</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8115,23 +8111,23 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Salandit</t>
+          <t>Skrelp</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8141,23 +8137,23 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Octillery</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8167,23 +8163,23 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>E2-2</t>
+          <t>EP2-2</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Challenge Road</t>
+          <t>Workout Sea</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Tentacool</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>45-52</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8193,101 +8189,101 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>E2-3</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Sandshrew</t>
+          <t>Exeggcute</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F320" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>E2-3</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Cubone</t>
+          <t>Flapple</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F321" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>E2-3</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Kangaskhan</t>
+          <t>Appletun</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F322" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>E2-3</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Torkoal</t>
+          <t>Wingull</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F323" t="n">
@@ -8297,213 +8293,205 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>E2-3</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Warm-Up Tunnel</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Skwovet</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F324" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>E2-4</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Potbottom Desert</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Sirfetch'd</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>82-89</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F325" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>E2-5</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Rock Peak Ruins</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Coalossal</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>E2-6</t>
+          <t>EP2-3</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Iceberg Ruins</t>
+          <t>Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Dubwool</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>50-55</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>E2-7</t>
+          <t>EP2-4</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Iron Ruins</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Dracovish</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>55-55</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>E2-8</t>
+          <t>EP2-4</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Split-Decision Ruins</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Honeycalm Island</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Regieleki</t>
+          <t>Petilil</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>55-55</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>E2-8</t>
+          <t>EP2-4</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Split-Decision Ruins</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Honeycalm Island</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Regidrago</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>55-55</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>EP2-4</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Smoochum</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>55-55</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8513,23 +8501,23 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>EP2-4</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Honeycalm Island</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Snom</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>55-55</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8539,49 +8527,49 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-1</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Mime Jr.</t>
+          <t>Orbeetle</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-95</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-1</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Butterfree</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-95</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8591,1989 +8579,1997 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-1</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Greedent</t>
+          <t>Whiscash</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-95</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-1</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Jynx</t>
+          <t>Barboach</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-95</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-1</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Corviknight</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-95</t>
         </is>
       </c>
       <c r="F337" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-1</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Cryogonal</t>
+          <t>Stunfisk</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-95</t>
         </is>
       </c>
       <c r="F338" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>E3-1</t>
+          <t>E1-1</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Slippery Slope</t>
+          <t>Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Amaura</t>
+          <t>Magikarp</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>70-95</t>
         </is>
       </c>
       <c r="F339" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr"/>
+          <t>Energy Plant</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Mime Jr.</t>
+          <t>Zacian</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E1-2</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr"/>
+          <t>Energy Plant</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Zamazenta</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Whismur</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Nidoran♂</t>
+          <t>Azurill</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Drakloak</t>
+          <t>Woobat</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Nidoran♀</t>
+          <t>Lickitung</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Karrablast</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="F346" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E2-1</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Brawlers' Cave</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Vanillite</t>
+          <t>Psyduck</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="F347" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>E3-2</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Old Cemetery</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Sinistea</t>
+          <t>Mienfoo</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F348" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Frosmoth</t>
+          <t>Skarmory</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F349" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Snom</t>
+          <t>Rockruff</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F350" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Dwebble</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F351" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>E3-3</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Path to the Peak</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Roggenrola</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F352" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>E3-4</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Crown Shrine</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Challenge Road</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Glastrier</t>
+          <t>Blipbug</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>E3-4</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Crown Shrine</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Challenge Road</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Spectrier</t>
+          <t>Salandit</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Carbink</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-2</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Challenge Road</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>73-79</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Sandshrew</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>77-82</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Omanyte</t>
+          <t>Cubone</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>77-82</t>
         </is>
       </c>
       <c r="F358" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Deino</t>
+          <t>Kangaskhan</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>77-82</t>
         </is>
       </c>
       <c r="F359" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Spheal</t>
+          <t>Torkoal</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>77-82</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-3</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Larvitar</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>77-82</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-4</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Potbottom Desert</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Feebas</t>
+          <t>Carkol</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>80-86</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>E4-1</t>
+          <t>E2-5</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Roaring-Sea Caves</t>
+          <t>Rock Peak Ruins</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Kabuto</t>
+          <t>Centiskorch</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>70-82</t>
+          <t>84-89</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-6</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Iceberg Ruins</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Gyarados</t>
+          <t>Hatterene</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>87-93</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-7</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Iron Ruins</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Dhelmise</t>
+          <t>Coalossal</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>91-95</t>
         </is>
       </c>
       <c r="F365" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-8</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr"/>
+          <t>Split-Decision Ruins</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Avalugg</t>
+          <t>Regieleki</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E2-8</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr"/>
+          <t>Split-Decision Ruins</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Tirtouga</t>
+          <t>Regidrago</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F367" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Lapras</t>
+          <t>Jynx</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Vanillish</t>
+          <t>Amaura</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Cryogonal</t>
+          <t>Mime Jr.</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F370" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>E4-2</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Frigid Sea</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Eiscue</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>80-92</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F371" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Bagon</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F372" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Gible</t>
+          <t>Snom</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F373" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Clefairy</t>
+          <t>Greedent</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F374" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Snorunt</t>
+          <t>Cryogonal</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F375" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-1</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Slippery Slope</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Smoochum</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F376" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Drakloak</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>E4-3</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Tunnel to the Top</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Carbink</t>
+          <t>Nidoran♂</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>90-100</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F378" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>E4-4</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Tower Summit</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Old Cemetery</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Calyrex</t>
+          <t>Nidoran♀</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>E4-4</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tower Summit</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
+          <t>Old Cemetery</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Eternatus</t>
+          <t>Vanillite</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Magnemite</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F381" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Dedenne</t>
+          <t>Sinistea</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F382" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Psyduck</t>
+          <t>Mime Jr.</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-2</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Old Cemetery</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Morpeko</t>
+          <t>Karrablast</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>E5-1</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Challenge Beach</t>
+          <t>Path to the Peak</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Frosmoth</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>70-76</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Path to the Peak</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Clauncher</t>
+          <t>Snom</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F387" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Path to the Peak</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Octillery</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-3</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Path to the Peak</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Tentacool</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-4</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr"/>
+          <t>Crown Shrine</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Skrelp</t>
+          <t>Glastrier</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E3-4</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr"/>
+          <t>Crown Shrine</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Remoraid</t>
+          <t>Spectrier</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Clawitzer</t>
+          <t>Omanyte</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Magikarp</t>
+          <t>Feebas</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Mantyke</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>E5-2</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Workout Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Dragalge</t>
+          <t>Carbink</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>74-80</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Exeggcute</t>
+          <t>Deino</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Flapple</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Appletun</t>
+          <t>Spheal</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Wingull</t>
+          <t>Kabuto</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-1</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Skwovet</t>
+          <t>Larvitar</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>70-80</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Dhelmise</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Avalugg</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>E5-3</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Stepping-Stone Sea</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Tirtouga</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>78-84</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>E5-4</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Lapras</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>82-89</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>E5-4</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Petilil</t>
+          <t>Gyarados</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>82-89</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F405" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>E5-4</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Blipbug</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>82-89</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>E5-4</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Cryogonal</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>82-89</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>E5-4</t>
+          <t>E4-2</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Honeycalm Island</t>
+          <t>Frigid Sea</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Eiscue</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>82-89</t>
+          <t>78-88</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Bagon</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Gible</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10583,23 +10579,23 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Skwovet</t>
+          <t>Clefairy</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10609,23 +10605,23 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Bouffalant</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10635,49 +10631,49 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Applin</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Wooper</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10687,23 +10683,23 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-3</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
+          <t>Tunnel to the Top</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Carbink</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>86-95</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -10713,59 +10709,67 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-4</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr"/>
+          <t>Tower Summit</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Shelmet</t>
+          <t>Calyrex</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>E5-5</t>
+          <t>E4-4</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Soothing Wetlands</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr"/>
+          <t>Tower Summit</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Dunsparce</t>
+          <t>Eternatus</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>87-93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -10781,7 +10785,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F418" t="n">
@@ -10791,7 +10795,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10807,7 +10811,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F419" t="n">
@@ -10817,7 +10821,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -10833,7 +10837,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F420" t="n">
@@ -10843,7 +10847,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -10859,7 +10863,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F421" t="n">
@@ -10869,7 +10873,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -10885,7 +10889,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F422" t="n">
@@ -10895,7 +10899,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -10911,7 +10915,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10921,7 +10925,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -10937,7 +10941,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10947,7 +10951,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>E5-6</t>
+          <t>E5-1</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -10963,7 +10967,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>91-97</t>
+          <t>70-84</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -10973,7 +10977,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -10989,7 +10993,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -10999,7 +11003,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11010,12 +11014,12 @@
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Carkol</t>
+          <t>Sableye</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11025,7 +11029,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11036,12 +11040,12 @@
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Sableye</t>
+          <t>Noivern</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -11051,7 +11055,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -11062,12 +11066,12 @@
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Noivern</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -11077,7 +11081,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -11088,12 +11092,12 @@
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Carbink</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -11103,7 +11107,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -11114,12 +11118,12 @@
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Carbink</t>
+          <t>Mawile</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -11129,7 +11133,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -11140,12 +11144,12 @@
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Mawile</t>
+          <t>Ferroseed</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -11155,7 +11159,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -11166,12 +11170,12 @@
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Ferroseed</t>
+          <t>Audino</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11181,7 +11185,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>E5-7</t>
+          <t>E5-2</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -11192,12 +11196,12 @@
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Audino</t>
+          <t>Carkol</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>95-100</t>
+          <t>82-95</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11207,7 +11211,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>E5-8</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -11237,7 +11241,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>E5-8</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -11267,7 +11271,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>E5-8</t>
+          <t>E5-3</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -11305,7 +11309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11525,7 +11529,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unlocks Route 5</t>
+          <t>Unlocks Route 5 &amp; Extra Paths (Fields of Honor)</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11954,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Unlocks Lake of Outrage</t>
+          <t>Unlocks Lake of Outrage &amp; Extra Paths (Challenge Beach)</t>
         </is>
       </c>
     </row>
@@ -12035,36 +12039,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Unlocks all 5 DLC Chains (Heroes, Regis, Steeds, Kings, Birds)</t>
+          <t>Unlocks Post-Game Paths (Slumbering Weald 2, Brawlers' Cave, Slippery Slope, Roaring-Sea Caves, Giant's Foot)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-1</t>
+          <t>Extra Challenge $P1-1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clear Slumbering Weald 2</t>
+          <t>Clear Fields of Honor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Unlocks Fields of Honor</t>
+          <t>Unlocks Soothing Wetlands</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-2</t>
+          <t>Extra Challenge $P1-2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clear Fields of Honor</t>
+          <t>Clear Soothing Wetlands</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12076,7 +12080,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-3</t>
+          <t>Extra Challenge $P1-3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12093,7 +12097,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-4</t>
+          <t>Extra Challenge $P1-4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12103,432 +12107,449 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unlocks Energy Plant</t>
+          <t>Unlocks Master Dojo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-5</t>
+          <t>Extra Challenge $P1-5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clear Energy Plant</t>
+          <t>Clear Master Dojo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Completed Heroes of Galar (Defeated Zacian &amp; Zamazenta)</t>
+          <t>Completed Isle of Armor Plains (Pre-League) (Defeated Kubfu)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-1</t>
+          <t>Extra Challenge $P2-1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clear Brawlers' Cave</t>
+          <t>Clear Challenge Beach</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Unlocks Challenge Road</t>
+          <t>Unlocks Workout Sea</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-2</t>
+          <t>Extra Challenge $P2-2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clear Challenge Road</t>
+          <t>Clear Workout Sea</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unlocks Warm-Up Tunnel</t>
+          <t>Unlocks Stepping-Stone Sea</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-3</t>
+          <t>Extra Challenge $P2-3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clear Warm-Up Tunnel</t>
+          <t>Clear Stepping-Stone Sea</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unlocks Potbottom Desert</t>
+          <t>Unlocks Honeycalm Island</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-4</t>
+          <t>Extra Challenge $P2-4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Clear Potbottom Desert</t>
+          <t>Clear Honeycalm Island</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unlocks Rock Peak Ruins</t>
+          <t>Completed Isle of Armor Sea (Pre-League)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-5</t>
+          <t>Extra Challenge $1-1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clear Rock Peak Ruins</t>
+          <t>Clear Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unlocks Iceberg Ruins</t>
+          <t>Unlocks Energy Plant</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-6</t>
+          <t>Extra Challenge $1-2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clear Iceberg Ruins</t>
+          <t>Clear Energy Plant</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Unlocks Iron Ruins</t>
+          <t>Completed Heroes of Galar (Post-League) (Defeated Zacian &amp; Zamazenta)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-7</t>
+          <t>Extra Challenge $2-1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clear Iron Ruins</t>
+          <t>Clear Brawlers' Cave</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unlocks Split-Decision Ruins</t>
+          <t>Unlocks Challenge Road</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-8</t>
+          <t>Extra Challenge $2-2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Clear Split-Decision Ruins</t>
+          <t>Clear Challenge Road</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Completed The Regis (Defeated Regieleki &amp; Regidrago)</t>
+          <t>Unlocks Warm-Up Tunnel</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-1</t>
+          <t>Extra Challenge $2-3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clear Slippery Slope</t>
+          <t>Clear Warm-Up Tunnel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Unlocks Old Cemetery</t>
+          <t>Unlocks Potbottom Desert</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-2</t>
+          <t>Extra Challenge $2-4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Clear Old Cemetery</t>
+          <t>Clear Potbottom Desert</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Unlocks Path to the Peak</t>
+          <t>Unlocks Rock Peak Ruins</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-3</t>
+          <t>Extra Challenge $2-5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Clear Path to the Peak</t>
+          <t>Clear Rock Peak Ruins</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unlocks Crown Shrine</t>
+          <t>Unlocks Iceberg Ruins</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-4</t>
+          <t>Extra Challenge $2-6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clear Crown Shrine</t>
+          <t>Clear Iceberg Ruins</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Completed The Steeds (Defeated Glastrier &amp; Spectrier)</t>
+          <t>Unlocks Iron Ruins</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-1</t>
+          <t>Extra Challenge $2-7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Clear Roaring-Sea Caves</t>
+          <t>Clear Iron Ruins</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unlocks Frigid Sea</t>
+          <t>Unlocks Split-Decision Ruins</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-2</t>
+          <t>Extra Challenge $2-8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Clear Frigid Sea</t>
+          <t>Clear Split-Decision Ruins</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Unlocks Tunnel to the Top</t>
+          <t>Completed The Regis (Post-League) (Defeated Regieleki &amp; Regidrago)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-3</t>
+          <t>Extra Challenge $3-1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Clear Tunnel to the Top</t>
+          <t>Clear Slippery Slope</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unlocks Tower Summit</t>
+          <t>Unlocks Old Cemetery</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-4</t>
+          <t>Extra Challenge $3-2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Clear Tower Summit</t>
+          <t>Clear Old Cemetery</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Completed The Kings (Defeated Calyrex &amp; Eternatus)</t>
+          <t>Unlocks Path to the Peak</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-1</t>
+          <t>Extra Challenge $3-3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Clear Challenge Beach</t>
+          <t>Clear Path to the Peak</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unlocks Workout Sea</t>
+          <t>Unlocks Crown Shrine</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-2</t>
+          <t>Extra Challenge $3-4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clear Workout Sea</t>
+          <t>Clear Crown Shrine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unlocks Stepping-Stone Sea</t>
+          <t>Completed The Steeds (Post-League) (Defeated Glastrier &amp; Spectrier)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-3</t>
+          <t>Extra Challenge $4-1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Clear Stepping-Stone Sea</t>
+          <t>Clear Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unlocks Honeycalm Island</t>
+          <t>Unlocks Frigid Sea</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-4</t>
+          <t>Extra Challenge $4-2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Clear Honeycalm Island</t>
+          <t>Clear Frigid Sea</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unlocks Soothing Wetlands</t>
+          <t>Unlocks Tunnel to the Top</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-5</t>
+          <t>Extra Challenge $4-3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Clear Soothing Wetlands</t>
+          <t>Clear Tunnel to the Top</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unlocks Giant's Foot</t>
+          <t>Unlocks Tower Summit</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-6</t>
+          <t>Extra Challenge $4-4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Clear Giant's Foot</t>
+          <t>Clear Tower Summit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unlocks Lakeside Cave</t>
+          <t>Completed The Kings (Post-League) (Defeated Calyrex &amp; Eternatus)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-7</t>
+          <t>Extra Challenge $5-1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Clear Lakeside Cave</t>
+          <t>Clear Giant's Foot</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unlocks Dyna Tree Hill</t>
+          <t>Unlocks Lakeside Cave</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-8</t>
+          <t>Extra Challenge $5-2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Clear Lakeside Cave</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Unlocks Dyna Tree Hill</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Extra Challenge $5-3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>Clear Dyna Tree Hill</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Completed The Legendary Birds (Defeated Articuno &amp; Zapdos &amp; Moltres)</t>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Completed The Legendary Birds (Post-League) (Defeated Articuno &amp; Zapdos &amp; Moltres)</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12576,7 +12597,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Gen 8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12586,7 +12607,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes (Evolution)</t>
+          <t>Yes (Evolution of Thwackey)</t>
         </is>
       </c>
     </row>
@@ -12598,7 +12619,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Gen 8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -12608,7 +12629,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yes (Evolution)</t>
+          <t>Yes (Evolution of Raboot)</t>
         </is>
       </c>
     </row>
@@ -12620,7 +12641,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Gen 8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12630,27 +12651,643 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yes (Evolution)</t>
+          <t>Yes (Evolution of Drizzile)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Eldegoss</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dubwool</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Boltund</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Toxtricity</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Clobbopus</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Grapploct</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Polteageist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Grimmsnarl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Obstagoon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cursola</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sirfetchd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mr Rime</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Runerigus</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alcremie</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dracozolt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Arctozolt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dracovish</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Arctovish</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dreepy</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dragapult</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Zarude</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wyrdeer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kleavor</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ursaluna</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Basculegion</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sneasler</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Overqwil</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Enamorus</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gen 8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Urshifu</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Fighting/Dark</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>No (Excluded per instructions)</t>
         </is>

--- a/Galar_Paths.xlsx
+++ b/Galar_Paths.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F437"/>
+  <dimension ref="A1:F444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11296,6 +11296,176 @@
       </c>
       <c r="F437" t="n">
         <v>33</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>29</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Route 9</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Clobbopus</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>30</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Lake of Outrage</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Dreepy</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>67-70</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>EP1-3</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Forest of Focus</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Zarude</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>22-28</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>19</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Route 6</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Dracozolt</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>42-46</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>19</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Route 6</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Arctozolt</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>42-46</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>19</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Route 6</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Dracovish</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>42-46</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>19</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Route 6</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Arctovish</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>42-46</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11309,7 +11479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12046,7 +12216,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Extra Challenge $P1-1</t>
+          <t>Extra Challenge A 1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12063,7 +12233,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Extra Challenge $P1-2</t>
+          <t>Extra Challenge A 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12080,7 +12250,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Extra Challenge $P1-3</t>
+          <t>Extra Challenge A 3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12097,7 +12267,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Extra Challenge $P1-4</t>
+          <t>Extra Challenge A 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12114,7 +12284,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Extra Challenge $P1-5</t>
+          <t>Extra Challenge A 5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12124,14 +12294,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Completed Isle of Armor Plains (Pre-League) (Defeated Kubfu)</t>
+          <t>Completed Isle of Armor Plains</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Extra Challenge $P2-1</t>
+          <t>Extra Challenge B 1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12148,7 +12318,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Extra Challenge $P2-2</t>
+          <t>Extra Challenge B 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12165,7 +12335,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Extra Challenge $P2-3</t>
+          <t>Extra Challenge B 3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12182,7 +12352,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Extra Challenge $P2-4</t>
+          <t>Extra Challenge B 4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12192,364 +12362,361 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Completed Isle of Armor Sea (Pre-League)</t>
+          <t>Completed Isle of Armor Sea</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-1</t>
+          <t>Extra Challenge C 1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clear Slumbering Weald 2</t>
+          <t>Clear Slippery Slope</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unlocks Energy Plant</t>
+          <t>Unlocks Path to the Peak</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Extra Challenge $1-2</t>
+          <t>Extra Challenge C 2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clear Energy Plant</t>
+          <t>Clear Path to the Peak</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Completed Heroes of Galar (Post-League) (Defeated Zacian &amp; Zamazenta)</t>
+          <t>Unlocks Old Cemetery</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-1</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Clear Brawlers' Cave</t>
-        </is>
-      </c>
+          <t>Extra Challenge C 3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unlocks Challenge Road</t>
+          <t>unlock Crown Shrine</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-2</t>
+          <t>Extra Challenge C 4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Clear Challenge Road</t>
+          <t>Capture Glastrier and Spectrier</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unlocks Warm-Up Tunnel</t>
+          <t>2 Masterball</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-3</t>
+          <t>Extra Challenge D 1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clear Warm-Up Tunnel</t>
+          <t>Clear Rock Peak Ruins</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Unlocks Potbottom Desert</t>
+          <t>Unlocks Iceberg Ruins</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-4</t>
+          <t>Extra Challenge D 2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Clear Potbottom Desert</t>
+          <t>Clear Iceberg Ruins</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Unlocks Rock Peak Ruins</t>
+          <t>Unlocks Iron Ruins</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-5</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Clear Rock Peak Ruins</t>
-        </is>
-      </c>
+          <t>Extra Challenge D 3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unlocks Iceberg Ruins</t>
+          <t>unlock Split-Decision Ruins</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-6</t>
+          <t>Extra Challenge D 4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clear Iceberg Ruins</t>
+          <t>Capture Regieleki and Regidrago</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unlocks Iron Ruins</t>
+          <t>2 Masterball</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-7</t>
+          <t>Extra Challenge E 1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Clear Iron Ruins</t>
+          <t>Clear Giant's Foot</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unlocks Split-Decision Ruins</t>
+          <t>Unlocks Lakeside Cave</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Extra Challenge $2-8</t>
+          <t>Extra Challenge E 2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Clear Split-Decision Ruins</t>
+          <t>Clear Lakeside Cave</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Completed The Regis (Post-League) (Defeated Regieleki &amp; Regidrago)</t>
+          <t>Unlocks Roaring-Sea Caves</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Clear Slippery Slope</t>
-        </is>
-      </c>
+          <t>Extra Challenge E 3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unlocks Old Cemetery</t>
+          <t>unlock Dyna Tree Hill</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-2</t>
+          <t>Extra Challenge E 4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Clear Old Cemetery</t>
+          <t>Capture Articuno Zapdos and Moltres</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Unlocks Path to the Peak</t>
+          <t>2 Masterball</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-3</t>
+          <t>Extra Challenge F 1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Clear Path to the Peak</t>
+          <t>Clear Slumbering Weald 2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unlocks Crown Shrine</t>
+          <t>Unlocks Brawlers' Cave</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Extra Challenge $3-4</t>
+          <t>Extra Challenge F 2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clear Crown Shrine</t>
+          <t>Clear Brawlers' Cave</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Completed The Steeds (Post-League) (Defeated Glastrier &amp; Spectrier)</t>
+          <t>Unlocks Challenge Road</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-1</t>
+          <t>Extra Challenge F 3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Clear Roaring-Sea Caves</t>
+          <t>Clear Challenge Road</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unlocks Frigid Sea</t>
+          <t>Unlocks Potbottom Desert</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-2</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Clear Frigid Sea</t>
-        </is>
-      </c>
+          <t>Extra Challenge F 4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unlocks Tunnel to the Top</t>
+          <t>unlock Energy Plant</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-3</t>
+          <t>Extra Challenge F 5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Clear Tunnel to the Top</t>
+          <t>Capture Zacian and Zamazenta</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unlocks Tower Summit</t>
+          <t>2 Masterball</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Extra Challenge $4-4</t>
+          <t>Extra Challenge G 1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Clear Tower Summit</t>
+          <t>Clear Frigid Sea</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Completed The Kings (Post-League) (Defeated Calyrex &amp; Eternatus)</t>
+          <t>Unlocks Tunnel to the Top</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-1</t>
+          <t>Extra Challenge G 2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Clear Giant's Foot</t>
+          <t>Clear Tunnel to the Top</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unlocks Lakeside Cave</t>
+          <t>Unlocks Roaring-Sea Caves</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-2</t>
+          <t>Extra Challenge G 3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Clear Lakeside Cave</t>
+          <t>Clear Roaring-Sea Caves</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Unlocks Dyna Tree Hill</t>
+          <t>Unlocks Brawlers' Cave</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Extra Challenge $5-3</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Clear Dyna Tree Hill</t>
-        </is>
-      </c>
+          <t>Extra Challenge G 4</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Completed The Legendary Birds (Post-League) (Defeated Articuno &amp; Zapdos &amp; Moltres)</t>
+          <t>unlock Tower Summit</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Extra Challenge G 5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Capture Calyrex and Eternaturs</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2 Masterball</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12607,7 +12774,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes (Evolution of Thwackey)</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12796,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yes (Evolution of Raboot)</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12818,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yes (Evolution of Drizzile)</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -12673,7 +12840,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Gossifleur)</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12862,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Wooloo)</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12884,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Yamper)</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12906,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Toxel)</t>
         </is>
       </c>
     </row>
@@ -12761,7 +12928,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12950,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Clobbopus)</t>
         </is>
       </c>
     </row>
@@ -12805,7 +12972,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Sinistea)</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12994,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Morgrem)</t>
         </is>
       </c>
     </row>
@@ -12849,7 +13016,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Linoone)</t>
         </is>
       </c>
     </row>
@@ -12871,7 +13038,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Corsola)</t>
         </is>
       </c>
     </row>
@@ -12893,7 +13060,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Farfetch'd)</t>
         </is>
       </c>
     </row>
@@ -12915,7 +13082,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Mr. Mime)</t>
         </is>
       </c>
     </row>
@@ -12937,7 +13104,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Yamask)</t>
         </is>
       </c>
     </row>
@@ -12959,7 +13126,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Milcery)</t>
         </is>
       </c>
     </row>
@@ -12981,7 +13148,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13170,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13192,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13214,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13069,7 +13236,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13258,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution of Drakloak)</t>
         </is>
       </c>
     </row>
@@ -13113,7 +13280,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13302,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13324,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13346,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13368,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13390,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13245,7 +13412,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
@@ -13267,29 +13434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Urshifu</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Fighting/Dark</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>No (Excluded per instructions)</t>
+          <t>Yes (Evolution)</t>
         </is>
       </c>
     </row>
